--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -1,37 +1,162 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARACATACA\Desktop\snies-monitor\data\novedades\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07509E29-38D6-4284-80B0-657ED87C6605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+  <si>
+    <t>CÓDIGO_INSTITUCIÓN</t>
+  </si>
+  <si>
+    <t>NOMBRE_INSTITUCIÓN</t>
+  </si>
+  <si>
+    <t>SECTOR</t>
+  </si>
+  <si>
+    <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
+  </si>
+  <si>
+    <t>MUNICIPIO_OFERTA_PROGRAMA</t>
+  </si>
+  <si>
+    <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
+  </si>
+  <si>
+    <t>NOMBRE_DEL_PROGRAMA</t>
+  </si>
+  <si>
+    <t>MODALIDAD</t>
+  </si>
+  <si>
+    <t>NÚMERO_CRÉDITOS</t>
+  </si>
+  <si>
+    <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
+  </si>
+  <si>
+    <t>PERIODICIDAD</t>
+  </si>
+  <si>
+    <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
+  </si>
+  <si>
+    <t>PERIODICIDAD_ADMISIONES</t>
+  </si>
+  <si>
+    <t>FECHA_DE_REGISTRO_EN_SNIES</t>
+  </si>
+  <si>
+    <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
+  </si>
+  <si>
+    <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
+  </si>
+  <si>
+    <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
+  </si>
+  <si>
+    <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
+  </si>
+  <si>
+    <t>NIVEL_DE_FORMACIÓN</t>
+  </si>
+  <si>
+    <t>PROGINSTI</t>
+  </si>
+  <si>
+    <t>FECHA_OBTENCION</t>
+  </si>
+  <si>
+    <t>DIVISIÓN UNINORTE</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>CORPORACION UNIVERSITARIA DE SABANETA - UNISABANETA</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>Antioquia</t>
+  </si>
+  <si>
+    <t>Sabaneta</t>
+  </si>
+  <si>
+    <t>DERECHO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Semestral</t>
+  </si>
+  <si>
+    <t>#########</t>
+  </si>
+  <si>
+    <t>Administración de Empresas y Derecho</t>
+  </si>
+  <si>
+    <t>Derecho</t>
+  </si>
+  <si>
+    <t>Derecho y afines</t>
+  </si>
+  <si>
+    <t>54290-148</t>
+  </si>
+  <si>
+    <t>Derecho, C. Política y Rel. Internacionales</t>
+  </si>
+  <si>
+    <t>Inactivo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,100 +171,56 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +258,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -211,6 +292,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,9 +327,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -420,127 +503,410 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CÓDIGO_INSTITUCIÓN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>NOMBRE_INSTITUCIÓN</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SECTOR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MUNICIPIO_OFERTA_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>NOMBRE_DEL_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>MODALIDAD</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>NÚMERO_CRÉDITOS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>PERIODICIDAD</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>PERIODICIDAD_ADMISIONES</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA_DE_REGISTRO_EN_SNIES</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>NIVEL_DE_FORMACIÓN</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA_DETECCION</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>DIVISIÓN UNINORTE</t>
-        </is>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>127</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2">
+        <v>54290</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2">
+        <v>148</v>
+      </c>
+      <c r="J2" s="2">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="2">
+        <v>4656800</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" s="3">
+        <v>45840</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100368D550A271F19479A1525D788665200" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d4cf941f41ec3e35b80febc5765ac407">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="53fd9aaf-26e0-4eca-bce0-e141f7e6a922" xmlns:ns3="88ed71e2-9521-4cf6-9606-4ef80891a900" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f35f6ef1ce299ba212a868296867058b" ns2:_="" ns3:_="">
+    <xsd:import namespace="53fd9aaf-26e0-4eca-bce0-e141f7e6a922"/>
+    <xsd:import namespace="88ed71e2-9521-4cf6-9606-4ef80891a900"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="53fd9aaf-26e0-4eca-bce0-e141f7e6a922" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a9bdeba3-8e6c-435e-977e-8b3dc5b5a0cd" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="88ed71e2-9521-4cf6-9606-4ef80891a900" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{646c4517-d8a9-444d-baac-c97787207726}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="88ed71e2-9521-4cf6-9606-4ef80891a900">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="53fd9aaf-26e0-4eca-bce0-e141f7e6a922">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="88ed71e2-9521-4cf6-9606-4ef80891a900" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8A268DC-BF07-48E3-8221-CB0F1497C846}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B85D5168-00BC-43DA-84BD-A484D0C079C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="53fd9aaf-26e0-4eca-bce0-e141f7e6a922"/>
+    <ds:schemaRef ds:uri="88ed71e2-9521-4cf6-9606-4ef80891a900"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B990EC-2640-46F8-B877-8BAA71720D84}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="53fd9aaf-26e0-4eca-bce0-e141f7e6a922"/>
+    <ds:schemaRef ds:uri="88ed71e2-9521-4cf6-9606-4ef80891a900"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,6 +636,109 @@
         </is>
       </c>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>106391</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MATEMÁTICAS APLICADAS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>17816650</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>42952</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,9 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -642,10 +639,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1728</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -699,7 +694,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>42952</v>
       </c>
       <c r="O3" t="inlineStr">
